--- a/ig/main/ValueSet-JDV-J153-TypeDiabete-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J153-TypeDiabete-ENS.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20230630120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J153-TypeDiabete-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J153-TypeDiabete-ENS.xlsx
@@ -83,7 +83,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J153-TypeDiabete-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J153-TypeDiabete-ENS.xlsx
@@ -7,9 +7,9 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R311-Regroup" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE-R310-CIM10AT" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE-R308-TAASIP" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
